--- a/Listing/COC04.xlsx
+++ b/Listing/COC04.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="181">
   <si>
     <t/>
   </si>
@@ -178,7 +178,7 @@
     <t>20072367</t>
   </si>
   <si>
-    <t>CADBURY CSHW NUT 57G</t>
+    <t>CADBURY CSHW NUT 52G</t>
   </si>
   <si>
     <t>8</t>
@@ -214,7 +214,7 @@
     <t>20039717</t>
   </si>
   <si>
-    <t>CADBURY DAIRY MLK 57</t>
+    <t>CADBURY DAIRY MLK 52</t>
   </si>
   <si>
     <t>20082194</t>
@@ -283,6 +283,12 @@
     <t>WNHAE STRW CHEESCAKE</t>
   </si>
   <si>
+    <t>20141002</t>
+  </si>
+  <si>
+    <t>WONHAE MTCHA BRY 30G</t>
+  </si>
+  <si>
     <t>20135661</t>
   </si>
   <si>
@@ -380,6 +386,12 @@
   </si>
   <si>
     <t>JLO GUMMY EGG 18G</t>
+  </si>
+  <si>
+    <t>20141453</t>
+  </si>
+  <si>
+    <t>JLO PERMEN LIPSTICK</t>
   </si>
   <si>
     <t>20139393</t>
@@ -934,7 +946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1719,7 +1731,7 @@
         <v>85</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -1736,10 +1748,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -1747,19 +1759,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>5</v>
@@ -1776,10 +1788,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -1796,10 +1808,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>5</v>
@@ -1816,10 +1828,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>5</v>
@@ -1827,19 +1839,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>5</v>
@@ -1856,10 +1868,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>5</v>
@@ -1876,10 +1888,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -1896,10 +1908,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -1916,10 +1928,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -1936,30 +1948,30 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>73</v>
@@ -1976,13 +1988,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1996,10 +2008,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2016,10 +2028,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2027,19 +2039,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2047,19 +2059,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="E56" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2076,10 +2088,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2096,10 +2108,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2116,10 +2128,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2136,10 +2148,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2147,19 +2159,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2167,19 +2179,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="E62" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>5</v>
@@ -2196,10 +2208,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2216,10 +2228,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>5</v>
@@ -2227,19 +2239,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -2247,39 +2259,39 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>152</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>154</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>5</v>
@@ -2287,62 +2299,62 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>152</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2356,13 +2368,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2376,13 +2388,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2396,50 +2408,50 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>5</v>
+        <v>156</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2456,10 +2468,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2476,12 +2488,52 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F79" s="1" t="s">
         <v>5</v>
       </c>
     </row>
